--- a/data/trans_dic/IP12B$oido-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$oido-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de oídos, otitis</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,78</t>
+          <t>0,0; 18,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,55</t>
+          <t>0,0; 28,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,02</t>
+          <t>0,0; 40,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,22</t>
+          <t>0,0; 58,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,65</t>
+          <t>0,0; 12,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 19,38</t>
+          <t>2,19; 18,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,01</t>
+          <t>0,0; 28,15</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,7</t>
+          <t>0,0; 27,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,07</t>
+          <t>0,0; 23,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 22,71</t>
+          <t>2,69; 26,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,67</t>
+          <t>0,0; 18,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,64</t>
+          <t>0,0; 22,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 16,01</t>
+          <t>1,81; 16,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 16,31</t>
+          <t>1,87; 15,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 13,37</t>
+          <t>1,51; 15,03</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,42</t>
+          <t>0,0; 40,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,8</t>
+          <t>0,0; 13,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,36</t>
+          <t>0,0; 19,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,15</t>
+          <t>0,0; 14,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,44</t>
+          <t>0,0; 6,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,1</t>
+          <t>0,0; 10,79</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,0</t>
+          <t>0,0; 44,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,76; 39,24</t>
+          <t>4,98; 43,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,99</t>
+          <t>0,0; 29,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,51</t>
+          <t>0,0; 32,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,83</t>
+          <t>0,0; 24,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,06</t>
+          <t>0,0; 27,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,75; 24,19</t>
+          <t>4,26; 23,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,43</t>
+          <t>0,0; 19,15</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 10,43</t>
+          <t>1,17; 10,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 15,36</t>
+          <t>3,48; 15,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,07; 12,18</t>
+          <t>2,1; 12,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 12,29</t>
+          <t>1,46; 13,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 14,11</t>
+          <t>2,62; 14,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 11,86</t>
+          <t>1,17; 10,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 9,77</t>
+          <t>2,02; 8,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,33; 11,9</t>
+          <t>4,02; 12,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,52; 10,2</t>
+          <t>2,19; 9,28</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1448</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1416</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1416</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3210</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3392</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4176</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4147</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2955</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>599; 5046</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4502</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1871</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1645</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2067</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1871</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3314</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4524</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>545; 5385</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3027</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3242</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>512; 4531</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>624; 5004</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>542; 5386</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3388</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2359</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3050</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3089</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 1881</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2970</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2947</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1312</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1689</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1420</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>4636</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1312</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3035</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>774; 6696</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4255</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3422</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5223</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4748</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1563; 8639</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4526</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1767</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4915</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3183</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2696</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4462</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>9216</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>5166</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>513; 4685</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2134; 9388</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1157; 6853</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>681; 6145</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1667; 8940</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>561; 5237</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1827; 8113</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>5025; 15153</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2257; 9558</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$oido-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$oido-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,73</t>
+          <t>0,0; 18,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,32 +693,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,77</t>
+          <t>0,0; 29,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,89</t>
+          <t>0,0; 43,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,26</t>
+          <t>0,0; 54,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,3</t>
+          <t>0,0; 11,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 18,45</t>
+          <t>2,22; 19,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,15</t>
+          <t>0,0; 30,03</t>
         </is>
       </c>
     </row>
@@ -788,27 +788,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,41</t>
+          <t>0,0; 27,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,58</t>
+          <t>0,0; 22,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 26,56</t>
+          <t>2,67; 23,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,75</t>
+          <t>0,0; 24,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,95</t>
+          <t>0,0; 23,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,17 +818,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 16,05</t>
+          <t>1,82; 15,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 15,02</t>
+          <t>1,88; 15,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 15,03</t>
+          <t>1,49; 13,54</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,92</t>
+          <t>0,0; 36,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,13</t>
+          <t>0,0; 15,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,73</t>
+          <t>0,0; 18,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,83</t>
+          <t>0,0; 6,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,79</t>
+          <t>0,0; 10,53</t>
         </is>
       </c>
     </row>
@@ -1008,27 +1008,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,33</t>
+          <t>0,0; 44,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,98; 43,06</t>
+          <t>4,89; 41,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,58</t>
+          <t>0,0; 30,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,61</t>
+          <t>0,0; 30,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,75</t>
+          <t>0,0; 25,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,38</t>
+          <t>0,0; 24,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 23,57</t>
+          <t>5,91; 24,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,15</t>
+          <t>0,0; 16,72</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,68</t>
+          <t>1,18; 11,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 15,32</t>
+          <t>3,4; 15,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 12,43</t>
+          <t>2,05; 12,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 13,16</t>
+          <t>1,49; 14,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 14,07</t>
+          <t>2,38; 13,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,94</t>
+          <t>1,16; 10,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,02; 8,96</t>
+          <t>1,92; 10,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 12,14</t>
+          <t>3,98; 11,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 9,28</t>
+          <t>2,51; 9,52</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3210</t>
+          <t>0; 3225</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1432,32 +1432,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3392</t>
+          <t>0; 3436</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4176</t>
+          <t>0; 4435</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4147</t>
+          <t>0; 3845</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2955</t>
+          <t>0; 2798</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>599; 5046</t>
+          <t>608; 5456</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4502</t>
+          <t>0; 4802</t>
         </is>
       </c>
     </row>
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3314</t>
+          <t>0; 3299</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4524</t>
+          <t>0; 4276</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>545; 5385</t>
+          <t>541; 4782</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3027</t>
+          <t>0; 3884</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3242</t>
+          <t>0; 3328</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>512; 4531</t>
+          <t>513; 4441</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>624; 5004</t>
+          <t>626; 5023</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>542; 5386</t>
+          <t>534; 4852</t>
         </is>
       </c>
     </row>
@@ -1758,32 +1758,32 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3388</t>
+          <t>0; 3004</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2359</t>
+          <t>0; 2358</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3050</t>
+          <t>0; 2516</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3089</t>
+          <t>0; 3852</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 1881</t>
+          <t>0; 1873</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2970</t>
+          <t>0; 2900</t>
         </is>
       </c>
     </row>
@@ -1911,42 +1911,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>774; 6696</t>
+          <t>761; 6488</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>0; 4342</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3229</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5278</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
           <t>0; 4255</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0; 3422</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>0; 5223</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0; 4748</t>
-        </is>
-      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1563; 8639</t>
+          <t>2167; 9147</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4526</t>
+          <t>0; 3951</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>513; 4685</t>
+          <t>519; 5013</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2134; 9388</t>
+          <t>2083; 9514</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1157; 6853</t>
+          <t>1132; 7010</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>681; 6145</t>
+          <t>697; 6587</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1667; 8940</t>
+          <t>1511; 8885</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>561; 5237</t>
+          <t>556; 5178</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1827; 8113</t>
+          <t>1742; 9092</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5025; 15153</t>
+          <t>4975; 14624</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2257; 9558</t>
+          <t>2582; 9799</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$oido-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$oido-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14,18%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19,9%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3,62%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14,18%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 28,55</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 37,02</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 60,22</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 18,81</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 18,78</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 29,15</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 43,43</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 54,01</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,64</t>
+          <t>0,0; 14,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 19,94</t>
+          <t>2,29; 19,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,03</t>
+          <t>0,0; 26,01</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>8,65%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>7,02%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>9,23%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,27</t>
+          <t>0,0; 18,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,29</t>
+          <t>0,0; 21,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,67; 23,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,06</t>
+          <t>0,0; 26,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,56</t>
+          <t>0,0; 24,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,7; 22,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 15,73</t>
+          <t>1,81; 16,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 15,08</t>
+          <t>1,87; 16,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 13,54</t>
+          <t>1,48; 13,37</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8,76%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 42,42</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 13,8</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 18,36</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 36,29</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 13,02</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 15,78</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,37</t>
+          <t>0,0; 17,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,8</t>
+          <t>0,0; 7,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,53</t>
+          <t>0,0; 10,1</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>10,52%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>18,95%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9,12%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,34</t>
+          <t>0,0; 28,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 41,72</t>
+          <t>0,0; 24,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,76</t>
+          <t>0,0; 45,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,01</t>
+          <t>4,76; 39,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 31,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,54</t>
+          <t>0,0; 25,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,91; 24,95</t>
+          <t>4,75; 24,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,72</t>
+          <t>0,0; 19,43</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,77%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6,77%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>4,03%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>8,02%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>5,77%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 11,42</t>
+          <t>1,46; 12,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,4; 15,52</t>
+          <t>2,35; 14,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 12,72</t>
+          <t>1,2; 11,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 14,1</t>
+          <t>1,18; 10,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 13,98</t>
+          <t>3,52; 15,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 10,82</t>
+          <t>2,07; 12,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 10,04</t>
+          <t>2,2; 9,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 11,71</t>
+          <t>4,33; 11,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 9,52</t>
+          <t>2,52; 10,2</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1448</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1416</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>621</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1448</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1416</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0; 3366</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3780</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4286</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3225</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3219</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3436</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4435</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3845</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2798</t>
+          <t>0; 3519</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>608; 5456</t>
+          <t>626; 5301</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4802</t>
+          <t>0; 4160</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1047</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1347</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1871</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3299</t>
+          <t>0; 3015</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4276</t>
+          <t>0; 3058</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>541; 4782</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3884</t>
+          <t>0; 3229</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3328</t>
+          <t>0; 4617</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>547; 4603</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>513; 4441</t>
+          <t>513; 4521</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>626; 5023</t>
+          <t>623; 5433</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>534; 4852</t>
+          <t>529; 4791</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>567</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0; 3512</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2501</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2927</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3004</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2358</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2516</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3852</t>
+          <t>0; 3597</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 1873</t>
+          <t>0; 2050</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2900</t>
+          <t>0; 2780</t>
         </is>
       </c>
     </row>
@@ -1805,27 +1805,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1689</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>720</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2947</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1312</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1689</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3035</t>
+          <t>0; 2992</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>761; 6488</t>
+          <t>0; 5240</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4342</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3229</t>
+          <t>0; 3081</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5278</t>
+          <t>740; 6102</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4602</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4255</t>
+          <t>0; 4345</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2167; 9147</t>
+          <t>1740; 8866</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3951</t>
+          <t>0; 4591</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2696</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>1767</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>4915</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3183</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2696</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>4301</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1983</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>519; 5013</t>
+          <t>682; 5742</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2083; 9514</t>
+          <t>1494; 8966</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1132; 7010</t>
+          <t>573; 5674</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>697; 6587</t>
+          <t>517; 4578</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1511; 8885</t>
+          <t>2155; 9416</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>556; 5178</t>
+          <t>1139; 6714</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1742; 9092</t>
+          <t>1988; 8848</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4975; 14624</t>
+          <t>5406; 14851</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2582; 9799</t>
+          <t>2598; 10505</t>
         </is>
       </c>
     </row>
